--- a/docs/02_design/機能設計書.xlsx
+++ b/docs/02_design/機能設計書.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ktakw\sg-mock-test-system\docs\02_design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BA1CB1A-731F-4490-9B55-2915AC8B8811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D60D376-53B6-4D12-B08F-7E56C5938CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="機能一覧" sheetId="1" r:id="rId1"/>
     <sheet name="機能設計書" sheetId="2" r:id="rId2"/>
+    <sheet name="業務フロー" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="188">
   <si>
     <t>機能ID</t>
   </si>
@@ -501,6 +502,108 @@
   <si>
     <t>状態管理必要</t>
     <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>【開始】</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   ↓</t>
+  </si>
+  <si>
+    <t>［トップ画面表示］</t>
+  </si>
+  <si>
+    <t>┌──────────────┐</t>
+  </si>
+  <si>
+    <t>│ 新規登録する？ │</t>
+  </si>
+  <si>
+    <t>└─────┬────────┘</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      ↓Yes                ↓No</t>
+  </si>
+  <si>
+    <t>［SCR-02 新規登録画面］   ［SCR-01 ログイン画面］</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      ↓                     ↓</t>
+  </si>
+  <si>
+    <t>［ユーザー情報入力］   ［ID・パスワード入力］</t>
+  </si>
+  <si>
+    <t>［登録処理］           ［認証処理］</t>
+  </si>
+  <si>
+    <t>┌──────────────┐   ┌──────────────┐</t>
+  </si>
+  <si>
+    <t>│ 登録成功？     │   │ 認証成功？     │</t>
+  </si>
+  <si>
+    <t>└─────┬────────┘   └─────┬────────┘</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      ↓Yes    ↓No           ↓Yes    ↓No</t>
+  </si>
+  <si>
+    <t>［ログインへ］［エラー表示］   ［SCR-03 マイページ］［エラー表示］</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      ↓            ↓              ↓            ↓</t>
+  </si>
+  <si>
+    <t>［ログイン処理］  ［再入力］      ↓        ［再入力］</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                         ↓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                ［書籍一覧表示］</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      ┌──────────────┬──────────────┬──────────────┐</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      ↓                    ↓                    ↓</t>
+  </si>
+  <si>
+    <t>［書籍登録］        ［書籍編集］        ［書籍削除］</t>
+  </si>
+  <si>
+    <t>［入力画面］        ［編集画面］        ［削除確認］</t>
+  </si>
+  <si>
+    <t>［登録処理］        ［更新処理］        ［削除処理］</t>
+  </si>
+  <si>
+    <t>┌────────┐       ┌────────┐       ┌────────┐</t>
+  </si>
+  <si>
+    <t>│成功？   │       │成功？   │       │成功？   │</t>
+  </si>
+  <si>
+    <t>└──┬─────┘       └──┬─────┘       └──┬─────┘</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   ↓Yes ↓No          ↓Yes ↓No          ↓Yes ↓No</t>
+  </si>
+  <si>
+    <t>［一覧へ］［エラー］ ［一覧へ］［エラー］ ［一覧へ］［エラー］</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        ↓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   ［マイページへ戻る］</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   ［ログアウト］</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      【終了】</t>
   </si>
 </sst>
 </file>
@@ -871,7 +974,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1010,23 +1113,17 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1334,19 +1431,19 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="22.2">
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="50" t="s">
         <v>144</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
     </row>
     <row r="3" spans="2:12">
       <c r="B3" s="23"/>
@@ -1425,7 +1522,7 @@
       <c r="K5" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="L5" s="50" t="s">
+      <c r="L5" s="48" t="s">
         <v>145</v>
       </c>
     </row>
@@ -1458,7 +1555,7 @@
       <c r="K6" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="L6" s="51"/>
+      <c r="L6" s="49"/>
     </row>
     <row r="7" spans="2:12" ht="30">
       <c r="B7" s="1"/>
@@ -1489,7 +1586,7 @@
       <c r="K7" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="L7" s="50" t="s">
+      <c r="L7" s="48" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1522,7 +1619,7 @@
       <c r="K8" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="L8" s="51" t="s">
+      <c r="L8" s="49" t="s">
         <v>147</v>
       </c>
     </row>
@@ -1555,7 +1652,7 @@
       <c r="K9" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="L9" s="50" t="s">
+      <c r="L9" s="48" t="s">
         <v>148</v>
       </c>
     </row>
@@ -1572,7 +1669,7 @@
       <c r="I10" s="41"/>
       <c r="J10" s="41"/>
       <c r="K10" s="41"/>
-      <c r="L10" s="52"/>
+      <c r="L10" s="41"/>
     </row>
     <row r="11" spans="2:12" ht="30">
       <c r="B11" s="1"/>
@@ -1603,7 +1700,7 @@
       <c r="K11" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="50"/>
+      <c r="L11" s="48"/>
     </row>
     <row r="12" spans="2:12" ht="45" customHeight="1">
       <c r="B12" s="15"/>
@@ -1634,7 +1731,7 @@
       <c r="K12" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="L12" s="51"/>
+      <c r="L12" s="49"/>
     </row>
     <row r="13" spans="2:12" ht="60" customHeight="1">
       <c r="B13" s="1"/>
@@ -1665,7 +1762,7 @@
       <c r="K13" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="L13" s="50"/>
+      <c r="L13" s="48"/>
     </row>
     <row r="14" spans="2:12" ht="30">
       <c r="B14" s="15"/>
@@ -1696,7 +1793,7 @@
       <c r="K14" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="L14" s="51"/>
+      <c r="L14" s="49"/>
     </row>
     <row r="15" spans="2:12">
       <c r="B15" s="42" t="s">
@@ -1711,7 +1808,7 @@
       <c r="I15" s="43"/>
       <c r="J15" s="43"/>
       <c r="K15" s="43"/>
-      <c r="L15" s="53"/>
+      <c r="L15" s="43"/>
     </row>
     <row r="16" spans="2:12" ht="30">
       <c r="B16" s="1"/>
@@ -1742,7 +1839,7 @@
       <c r="K16" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="L16" s="50"/>
+      <c r="L16" s="48"/>
     </row>
     <row r="17" spans="2:12" ht="30">
       <c r="B17" s="15"/>
@@ -1773,7 +1870,7 @@
       <c r="K17" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="L17" s="51"/>
+      <c r="L17" s="49"/>
     </row>
     <row r="18" spans="2:12">
       <c r="B18" s="1"/>
@@ -1804,7 +1901,7 @@
       <c r="K18" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="L18" s="50"/>
+      <c r="L18" s="48"/>
     </row>
     <row r="19" spans="2:12" ht="30">
       <c r="B19" s="15"/>
@@ -1835,7 +1932,7 @@
       <c r="K19" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="L19" s="51"/>
+      <c r="L19" s="49"/>
     </row>
     <row r="20" spans="2:12" ht="30">
       <c r="B20" s="1"/>
@@ -1866,7 +1963,7 @@
       <c r="K20" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="L20" s="50"/>
+      <c r="L20" s="48"/>
     </row>
     <row r="21" spans="2:12" ht="32.4">
       <c r="B21" s="15"/>
@@ -1897,7 +1994,7 @@
       <c r="K21" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="L21" s="51"/>
+      <c r="L21" s="49"/>
     </row>
     <row r="22" spans="2:12">
       <c r="B22" s="1"/>
@@ -1928,7 +2025,7 @@
       <c r="K22" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="L22" s="50"/>
+      <c r="L22" s="48"/>
     </row>
     <row r="23" spans="2:12">
       <c r="B23" s="44" t="s">
@@ -1974,7 +2071,7 @@
       <c r="K24" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="L24" s="50"/>
+      <c r="L24" s="48"/>
     </row>
     <row r="25" spans="2:12">
       <c r="B25" s="8"/>
@@ -2005,7 +2102,7 @@
       <c r="K25" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="L25" s="51"/>
+      <c r="L25" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2036,19 +2133,19 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="22.2">
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="50" t="s">
         <v>144</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
     </row>
     <row r="3" spans="2:12">
       <c r="B3" s="23"/>
@@ -2716,4 +2813,230 @@
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91979041-D559-4369-B044-F42A36666AF5}">
+  <dimension ref="B2:B44"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="2" spans="2:2">
+      <c r="B2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2">
+      <c r="B3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2">
+      <c r="B4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2">
+      <c r="B5" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2">
+      <c r="B6" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2">
+      <c r="B7" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2">
+      <c r="B8" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2">
+      <c r="B9" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2">
+      <c r="B10" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2">
+      <c r="B11" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2">
+      <c r="B12" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2">
+      <c r="B13" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2">
+      <c r="B14" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2">
+      <c r="B15" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2">
+      <c r="B16" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2">
+      <c r="B23" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2">
+      <c r="B30" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2">
+      <c r="B31" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2">
+      <c r="B41" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2">
+      <c r="B42" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2">
+      <c r="B43" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2">
+      <c r="B44" t="s">
+        <v>187</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/docs/02_design/機能設計書.xlsx
+++ b/docs/02_design/機能設計書.xlsx
@@ -1,33 +1,272 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ktakw\sg-mock-test-system\docs\02_design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D60D376-53B6-4D12-B08F-7E56C5938CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{247A8AF5-EA72-4D08-A759-C74842EE3E5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="機能一覧" sheetId="1" r:id="rId1"/>
     <sheet name="機能設計書" sheetId="2" r:id="rId2"/>
     <sheet name="業務フロー" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="216">
+  <si>
+    <t>業務フロー  ─  SG 模擬試験システム</t>
+  </si>
+  <si>
+    <t>■ ① アカウント機能（Account）</t>
+  </si>
+  <si>
+    <t>受講者</t>
+  </si>
+  <si>
+    <t>システム</t>
+  </si>
+  <si>
+    <t>講師</t>
+  </si>
+  <si>
+    <t>【開始】 トップ画面アクセス</t>
+  </si>
+  <si>
+    <t>↓</t>
+  </si>
+  <si>
+    <t>新規登録を選択
+（SCR-02 新規登録画面）</t>
+  </si>
+  <si>
+    <t>名前・メール・パスワード 入力</t>
+  </si>
+  <si>
+    <t>↓ 送信</t>
+  </si>
+  <si>
+    <t>入力チェック
+→ メール重複確認
+→ パスワードハッシュ化
+→ DB登録 (A-03)</t>
+  </si>
+  <si>
+    <t>↓ 成功 / ✕ エラー表示 → 再入力</t>
+  </si>
+  <si>
+    <t>ログイン画面へ遷移
+（登録完了メッセージ表示）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ▶ ログインフロー（A-01）</t>
+  </si>
+  <si>
+    <t>メールアドレス・パスワード 入力
+（SCR-01 ログイン画面）</t>
+  </si>
+  <si>
+    <t>入力値チェック
+→ ユーザー取得
+→ パスワード照合
+→ セッション生成 (A-01)</t>
+  </si>
+  <si>
+    <t>↓ 成功 / ✕ 認証失敗エラー → 再入力</t>
+  </si>
+  <si>
+    <t>マイページ (SCR-03) へ遷移</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ▶ ログアウトフロー（A-02）</t>
+  </si>
+  <si>
+    <t>ログアウト操作</t>
+  </si>
+  <si>
+    <t>セッション無効化
+→ 認証情報削除 (A-02)</t>
+  </si>
+  <si>
+    <t>ログイン画面へ遷移</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ▶ アカウント更新（A-05）／削除（A-04）</t>
+  </si>
+  <si>
+    <t>プロフィール編集画面で
+情報変更・送信 (A-05)</t>
+  </si>
+  <si>
+    <t>対象ユーザー選択
+→ 削除実行 (A-04)</t>
+  </si>
+  <si>
+    <t>入力チェック → 重複確認
+→ 更新 or 論理削除処理</t>
+  </si>
+  <si>
+    <t>更新完了メッセージ</t>
+  </si>
+  <si>
+    <t>削除完了メッセージ / 一覧へ</t>
+  </si>
+  <si>
+    <t>■ ② 受験前機能（Preparation）</t>
+  </si>
+  <si>
+    <t>受験予定日・開始時間 を選択
+（SCR-PRE-01）</t>
+  </si>
+  <si>
+    <t>↓ 登録送信</t>
+  </si>
+  <si>
+    <t>入力チェック
+→ 過去日時確認
+→ 重複確認
+→ DB登録 (PRE-01)</t>
+  </si>
+  <si>
+    <t>↓ 登録完了</t>
+  </si>
+  <si>
+    <t>講師へ報告 (PRE-02)
+→ 報告完了メッセージ</t>
+  </si>
+  <si>
+    <t>↓ 報告</t>
+  </si>
+  <si>
+    <t>登録済み確認
+→ 報告登録
+→ ステータス更新 (PRE-02)</t>
+  </si>
+  <si>
+    <t>↓ 報告通知</t>
+  </si>
+  <si>
+    <t>受験予定一覧を確認
+（PRE-03）</t>
+  </si>
+  <si>
+    <t>↓ 承認操作</t>
+  </si>
+  <si>
+    <t>報告済み確認
+→ ステータス更新
+→ 通知登録 (PRE-04)</t>
+  </si>
+  <si>
+    <t>↓ 受理完了通知</t>
+  </si>
+  <si>
+    <t>受験予定 受理完了</t>
+  </si>
+  <si>
+    <t>受理完了メッセージ</t>
+  </si>
+  <si>
+    <t>■ ③ 受験機能（Execute）</t>
+  </si>
+  <si>
+    <t>試験開始操作
+（受験可否・時間帯を確認済み）</t>
+  </si>
+  <si>
+    <t>受験可否確認
+→ 問題取得
+→ セッション開始 (EXE-01)</t>
+  </si>
+  <si>
+    <t>↓ 問題画面表示</t>
+  </si>
+  <si>
+    <t>回答入力</t>
+  </si>
+  <si>
+    <t>タイマー管理 (EXE-02)
+開始時刻記録 → 終了時刻算出
+→ 自動終了</t>
+  </si>
+  <si>
+    <t>↓ 送信 or 時間切れ自動終了</t>
+  </si>
+  <si>
+    <t>回答採点
+→ 結果算出
+→ DB保存 (EXE-03)</t>
+  </si>
+  <si>
+    <t>↓ 結果表示</t>
+  </si>
+  <si>
+    <t>得点・正誤確認 (EXE-03)
+解答・解説確認 (EXE-04)</t>
+  </si>
+  <si>
+    <t>↓ 完了報告操作</t>
+  </si>
+  <si>
+    <t>完了確認
+→ ステータス更新
+→ 報告登録 (EXE-05)</t>
+  </si>
+  <si>
+    <t>↓ 完了通知</t>
+  </si>
+  <si>
+    <t>試験結果一覧確認
+（EXE-06）</t>
+  </si>
+  <si>
+    <t>報告確認
+→ ステータス更新
+→ 通知 (EXE-07)</t>
+  </si>
+  <si>
+    <t>↓ 承認完了通知</t>
+  </si>
+  <si>
+    <t>承認完了</t>
+  </si>
+  <si>
+    <t>承認完了メッセージ</t>
+  </si>
+  <si>
+    <t>■ ④ 受験後機能（History）</t>
+  </si>
+  <si>
+    <t>受験履歴を閲覧
+（HIS-01 本人のみ）</t>
+  </si>
+  <si>
+    <t>試験完了時に自動保存
+→ 履歴取得 → 表示 (HIS-01)</t>
+  </si>
+  <si>
+    <t>全受講者の履歴一覧確認
+（HIS-02 / フィルタ・検索可）</t>
+  </si>
+  <si>
+    <t>DB取得 → 検索
+→ 一覧表示 (HIS-02)</t>
+  </si>
+  <si>
+    <t>【終了】 ログアウト (A-02)</t>
+  </si>
+  <si>
+    <t>機能一覧  ─  SG 模擬試験システム</t>
+  </si>
   <si>
     <t>機能ID</t>
   </si>
@@ -57,10 +296,9 @@
   </si>
   <si>
     <t>CRUD要素</t>
-    <rPh sb="4" eb="6">
-      <t>ヨウソ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>■ アカウント機能</t>
   </si>
   <si>
     <t>A-01</t>
@@ -90,6 +328,9 @@
     <t>全員</t>
   </si>
   <si>
+    <t>R</t>
+  </si>
+  <si>
     <t>A-02</t>
   </si>
   <si>
@@ -99,9 +340,6 @@
     <t>ユーザーがログアウトする</t>
   </si>
   <si>
-    <t>ログアウト操作</t>
-  </si>
-  <si>
     <t>ログイン画面</t>
   </si>
   <si>
@@ -138,6 +376,9 @@
     <t>パスワードはハッシュ化</t>
   </si>
   <si>
+    <t>C</t>
+  </si>
+  <si>
     <t>A-04</t>
   </si>
   <si>
@@ -162,7 +403,7 @@
     <t>論理削除推奨</t>
   </si>
   <si>
-    <t>講師</t>
+    <t>D</t>
   </si>
   <si>
     <t>A-05</t>
@@ -177,9 +418,6 @@
     <t>名前、メール、パスワード等</t>
   </si>
   <si>
-    <t>更新完了メッセージ</t>
-  </si>
-  <si>
     <t>入力チェック→ユーザー確認→重複チェック→更新処理</t>
   </si>
   <si>
@@ -189,6 +427,12 @@
     <t>パスワード変更時ハッシュ化</t>
   </si>
   <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>■ 受験前機能（Preparation）</t>
+  </si>
+  <si>
     <t>PRE-01</t>
   </si>
   <si>
@@ -213,9 +457,6 @@
     <t>時間制限あり</t>
   </si>
   <si>
-    <t>受講者</t>
-  </si>
-  <si>
     <t>PRE-02</t>
   </si>
   <si>
@@ -276,9 +517,6 @@
     <t>対象データ選択</t>
   </si>
   <si>
-    <t>受理完了メッセージ</t>
-  </si>
-  <si>
     <t>報告済確認→ステータス更新→通知登録</t>
   </si>
   <si>
@@ -288,6 +526,9 @@
     <t>通知機能あり</t>
   </si>
   <si>
+    <t>■ 受験機能（Execute）</t>
+  </si>
+  <si>
     <t>EXE-01</t>
   </si>
   <si>
@@ -309,6 +550,9 @@
     <t>受験時間外不可、再受験制御あり</t>
   </si>
   <si>
+    <t>状態管理必要</t>
+  </si>
+  <si>
     <t>EXE-02</t>
   </si>
   <si>
@@ -426,6 +670,9 @@
     <t>通知あり</t>
   </si>
   <si>
+    <t>■ 受験後機能（History）</t>
+  </si>
+  <si>
     <t>HIS-01</t>
   </si>
   <si>
@@ -463,154 +710,13 @@
   </si>
   <si>
     <t>フィルタ可能</t>
-  </si>
-  <si>
-    <t>機能一覧  ─  SG 模擬試験システム</t>
-    <rPh sb="0" eb="2">
-      <t>キノウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>U</t>
-  </si>
-  <si>
-    <t>■ アカウント機能</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>■ 受験前機能（Preparation）</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>■ 受験機能（Execute）</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>■ 受験後機能（History）</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>状態管理必要</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>【開始】</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   ↓</t>
-  </si>
-  <si>
-    <t>［トップ画面表示］</t>
-  </si>
-  <si>
-    <t>┌──────────────┐</t>
-  </si>
-  <si>
-    <t>│ 新規登録する？ │</t>
-  </si>
-  <si>
-    <t>└─────┬────────┘</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      ↓Yes                ↓No</t>
-  </si>
-  <si>
-    <t>［SCR-02 新規登録画面］   ［SCR-01 ログイン画面］</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      ↓                     ↓</t>
-  </si>
-  <si>
-    <t>［ユーザー情報入力］   ［ID・パスワード入力］</t>
-  </si>
-  <si>
-    <t>［登録処理］           ［認証処理］</t>
-  </si>
-  <si>
-    <t>┌──────────────┐   ┌──────────────┐</t>
-  </si>
-  <si>
-    <t>│ 登録成功？     │   │ 認証成功？     │</t>
-  </si>
-  <si>
-    <t>└─────┬────────┘   └─────┬────────┘</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      ↓Yes    ↓No           ↓Yes    ↓No</t>
-  </si>
-  <si>
-    <t>［ログインへ］［エラー表示］   ［SCR-03 マイページ］［エラー表示］</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      ↓            ↓              ↓            ↓</t>
-  </si>
-  <si>
-    <t>［ログイン処理］  ［再入力］      ↓        ［再入力］</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                         ↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                ［書籍一覧表示］</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      ┌──────────────┬──────────────┬──────────────┐</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      ↓                    ↓                    ↓</t>
-  </si>
-  <si>
-    <t>［書籍登録］        ［書籍編集］        ［書籍削除］</t>
-  </si>
-  <si>
-    <t>［入力画面］        ［編集画面］        ［削除確認］</t>
-  </si>
-  <si>
-    <t>［登録処理］        ［更新処理］        ［削除処理］</t>
-  </si>
-  <si>
-    <t>┌────────┐       ┌────────┐       ┌────────┐</t>
-  </si>
-  <si>
-    <t>│成功？   │       │成功？   │       │成功？   │</t>
-  </si>
-  <si>
-    <t>└──┬─────┘       └──┬─────┘       └──┬─────┘</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   ↓Yes ↓No          ↓Yes ↓No          ↓Yes ↓No</t>
-  </si>
-  <si>
-    <t>［一覧へ］［エラー］ ［一覧へ］［エラー］ ［一覧へ］［エラー］</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        ↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   ［マイページへ戻る］</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   ［ログアウト］</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      【終了】</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -630,13 +736,6 @@
       <sz val="6"/>
       <name val="Yu Gothic"/>
       <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="6"/>
-      <name val="Yu Gothic"/>
-      <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -732,8 +831,46 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF666666"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -808,8 +945,23 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF444441"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFEFEF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F5F5"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -967,6 +1119,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -974,171 +1141,185 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
-    <cellStyle name="標準 2" xfId="1" xr:uid="{A327F2B8-8083-406B-96B6-51B359591D24}"/>
+    <cellStyle name="標準 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <mruColors>
-      <color rgb="FFF0EFEB"/>
-      <color rgb="FFEEEDFE"/>
-      <color rgb="FF444441"/>
-    </mruColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1413,6 +1594,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <tabColor theme="5" tint="0.59999389629810485"/>
+  </sheetPr>
   <dimension ref="B2:L25"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelCol="1"/>
   <cols>
@@ -1430,57 +1614,57 @@
     <col min="12" max="12" width="8.8984375" bestFit="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="22.2">
-      <c r="B2" s="50" t="s">
-        <v>144</v>
-      </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
+    <row r="2" spans="2:12" ht="22.2" customHeight="1">
+      <c r="B2" s="54" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
     </row>
     <row r="3" spans="2:12">
       <c r="B3" s="23"/>
       <c r="C3" s="23" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="E3" s="24" t="s">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="F3" s="24" t="s">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="G3" s="24" t="s">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="H3" s="24" t="s">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="I3" s="24" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="J3" s="24" t="s">
-        <v>7</v>
+        <v>75</v>
       </c>
       <c r="K3" s="24" t="s">
-        <v>8</v>
+        <v>76</v>
       </c>
       <c r="L3" s="24" t="s">
-        <v>9</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="2:12">
       <c r="B4" s="46" t="s">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="C4" s="47"/>
       <c r="D4" s="47"/>
@@ -1493,172 +1677,172 @@
       <c r="K4" s="47"/>
       <c r="L4" s="47"/>
     </row>
-    <row r="5" spans="2:12" ht="30">
+    <row r="5" spans="2:12" ht="30" customHeight="1">
       <c r="B5" s="1"/>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>14</v>
+        <v>83</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
       <c r="I5" s="38" t="s">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="J5" s="38" t="s">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="K5" s="38" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="L5" s="48" t="s">
-        <v>145</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="2:12">
       <c r="B6" s="31"/>
       <c r="C6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F6" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="33" t="s">
-        <v>22</v>
-      </c>
       <c r="G6" s="34" t="s">
-        <v>23</v>
+        <v>92</v>
       </c>
       <c r="H6" s="35" t="s">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="I6" s="39" t="s">
-        <v>25</v>
+        <v>94</v>
       </c>
       <c r="J6" s="39" t="s">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="K6" s="39" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="L6" s="49"/>
     </row>
-    <row r="7" spans="2:12" ht="30">
+    <row r="7" spans="2:12" ht="30" customHeight="1">
       <c r="B7" s="1"/>
       <c r="C7" s="2" t="s">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>28</v>
+        <v>97</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>31</v>
+        <v>100</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>32</v>
+        <v>101</v>
       </c>
       <c r="I7" s="38" t="s">
-        <v>33</v>
+        <v>102</v>
       </c>
       <c r="J7" s="38" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="K7" s="38" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="L7" s="48" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" ht="30">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="30" customHeight="1">
       <c r="B8" s="31"/>
       <c r="C8" s="2" t="s">
-        <v>35</v>
+        <v>105</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>36</v>
+        <v>106</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>37</v>
+        <v>107</v>
       </c>
       <c r="F8" s="33" t="s">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>39</v>
+        <v>109</v>
       </c>
       <c r="H8" s="35" t="s">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="I8" s="39" t="s">
-        <v>41</v>
+        <v>111</v>
       </c>
       <c r="J8" s="39" t="s">
-        <v>42</v>
+        <v>112</v>
       </c>
       <c r="K8" s="39" t="s">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="L8" s="49" t="s">
-        <v>147</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="60" customHeight="1">
       <c r="B9" s="25"/>
       <c r="C9" s="2" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>45</v>
+        <v>115</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>46</v>
+        <v>116</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>47</v>
+        <v>117</v>
       </c>
       <c r="G9" s="28" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="H9" s="29" t="s">
-        <v>49</v>
+        <v>118</v>
       </c>
       <c r="I9" s="38" t="s">
-        <v>50</v>
+        <v>119</v>
       </c>
       <c r="J9" s="38" t="s">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="K9" s="38" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="L9" s="48" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="2:12">
       <c r="B10" s="40" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="C10" s="41"/>
       <c r="D10" s="41"/>
@@ -1671,133 +1855,133 @@
       <c r="K10" s="41"/>
       <c r="L10" s="41"/>
     </row>
-    <row r="11" spans="2:12" ht="30">
+    <row r="11" spans="2:12" ht="30" customHeight="1">
       <c r="B11" s="1"/>
       <c r="C11" s="13" t="s">
-        <v>52</v>
+        <v>123</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>53</v>
+        <v>124</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>54</v>
+        <v>125</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>55</v>
+        <v>126</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>56</v>
+        <v>127</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>57</v>
+        <v>128</v>
       </c>
       <c r="I11" s="38" t="s">
-        <v>58</v>
+        <v>129</v>
       </c>
       <c r="J11" s="38" t="s">
-        <v>59</v>
+        <v>130</v>
       </c>
       <c r="K11" s="38" t="s">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="L11" s="48"/>
     </row>
     <row r="12" spans="2:12" ht="45" customHeight="1">
       <c r="B12" s="15"/>
       <c r="C12" s="13" t="s">
-        <v>61</v>
+        <v>131</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>62</v>
+        <v>132</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>63</v>
+        <v>133</v>
       </c>
       <c r="F12" s="33" t="s">
-        <v>64</v>
+        <v>134</v>
       </c>
       <c r="G12" s="34" t="s">
-        <v>65</v>
+        <v>135</v>
       </c>
       <c r="H12" s="35" t="s">
-        <v>66</v>
+        <v>136</v>
       </c>
       <c r="I12" s="39" t="s">
-        <v>67</v>
+        <v>137</v>
       </c>
       <c r="J12" s="39" t="s">
-        <v>68</v>
+        <v>138</v>
       </c>
       <c r="K12" s="39" t="s">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="L12" s="49"/>
     </row>
     <row r="13" spans="2:12" ht="60" customHeight="1">
       <c r="B13" s="1"/>
       <c r="C13" s="13" t="s">
-        <v>69</v>
+        <v>139</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>71</v>
+        <v>141</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>72</v>
+        <v>142</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>73</v>
+        <v>143</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>74</v>
+        <v>144</v>
       </c>
       <c r="I13" s="38" t="s">
-        <v>75</v>
+        <v>145</v>
       </c>
       <c r="J13" s="38" t="s">
-        <v>76</v>
+        <v>146</v>
       </c>
       <c r="K13" s="38" t="s">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="L13" s="48"/>
     </row>
-    <row r="14" spans="2:12" ht="30">
+    <row r="14" spans="2:12" ht="30" customHeight="1">
       <c r="B14" s="15"/>
       <c r="C14" s="13" t="s">
-        <v>77</v>
+        <v>147</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>79</v>
+        <v>149</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="I14" s="39" t="s">
-        <v>83</v>
+        <v>152</v>
       </c>
       <c r="J14" s="39" t="s">
-        <v>84</v>
+        <v>153</v>
       </c>
       <c r="K14" s="39" t="s">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="L14" s="49"/>
     </row>
     <row r="15" spans="2:12">
       <c r="B15" s="42" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C15" s="43"/>
       <c r="D15" s="43"/>
@@ -1810,226 +1994,226 @@
       <c r="K15" s="43"/>
       <c r="L15" s="43"/>
     </row>
-    <row r="16" spans="2:12" ht="30">
+    <row r="16" spans="2:12" ht="30" customHeight="1">
       <c r="B16" s="1"/>
       <c r="C16" s="17" t="s">
-        <v>85</v>
+        <v>155</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>86</v>
+        <v>156</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>87</v>
+        <v>157</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>88</v>
+        <v>158</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>89</v>
+        <v>159</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="I16" s="38" t="s">
-        <v>91</v>
+        <v>161</v>
       </c>
       <c r="J16" s="38" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="K16" s="38" t="s">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="L16" s="48"/>
     </row>
-    <row r="17" spans="2:12" ht="30">
+    <row r="17" spans="2:12" ht="30" customHeight="1">
       <c r="B17" s="15"/>
       <c r="C17" s="17" t="s">
-        <v>92</v>
+        <v>163</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>93</v>
+        <v>164</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>94</v>
+        <v>165</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>95</v>
+        <v>166</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>96</v>
+        <v>167</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>97</v>
+        <v>168</v>
       </c>
       <c r="I17" s="39" t="s">
-        <v>98</v>
+        <v>169</v>
       </c>
       <c r="J17" s="39" t="s">
-        <v>99</v>
+        <v>170</v>
       </c>
       <c r="K17" s="39" t="s">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="L17" s="49"/>
     </row>
     <row r="18" spans="2:12">
       <c r="B18" s="1"/>
       <c r="C18" s="17" t="s">
-        <v>100</v>
+        <v>171</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>101</v>
+        <v>172</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>72</v>
+        <v>142</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>103</v>
+        <v>174</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>104</v>
+        <v>175</v>
       </c>
       <c r="I18" s="38" t="s">
-        <v>105</v>
+        <v>176</v>
       </c>
       <c r="J18" s="38" t="s">
-        <v>106</v>
+        <v>177</v>
       </c>
       <c r="K18" s="38" t="s">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="L18" s="48"/>
     </row>
-    <row r="19" spans="2:12" ht="30">
+    <row r="19" spans="2:12" ht="30" customHeight="1">
       <c r="B19" s="15"/>
       <c r="C19" s="17" t="s">
-        <v>107</v>
+        <v>178</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>108</v>
+        <v>179</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>109</v>
+        <v>180</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>72</v>
+        <v>142</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>110</v>
+        <v>181</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>111</v>
+        <v>182</v>
       </c>
       <c r="I19" s="39" t="s">
-        <v>112</v>
+        <v>183</v>
       </c>
       <c r="J19" s="39" t="s">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="K19" s="39" t="s">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="L19" s="49"/>
     </row>
-    <row r="20" spans="2:12" ht="30">
+    <row r="20" spans="2:12" ht="30" customHeight="1">
       <c r="B20" s="1"/>
       <c r="C20" s="17" t="s">
-        <v>113</v>
+        <v>184</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>114</v>
+        <v>185</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>115</v>
+        <v>186</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>116</v>
+        <v>187</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>117</v>
+        <v>188</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>118</v>
+        <v>189</v>
       </c>
       <c r="I20" s="38" t="s">
-        <v>119</v>
+        <v>190</v>
       </c>
       <c r="J20" s="38" t="s">
-        <v>68</v>
+        <v>138</v>
       </c>
       <c r="K20" s="38" t="s">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="L20" s="48"/>
     </row>
-    <row r="21" spans="2:12" ht="32.4">
+    <row r="21" spans="2:12" ht="32.4" customHeight="1">
       <c r="B21" s="15"/>
       <c r="C21" s="17" t="s">
-        <v>120</v>
+        <v>191</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>121</v>
+        <v>192</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>122</v>
+        <v>193</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>72</v>
+        <v>142</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>73</v>
+        <v>143</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>123</v>
+        <v>194</v>
       </c>
       <c r="I21" s="39" t="s">
-        <v>75</v>
+        <v>145</v>
       </c>
       <c r="J21" s="39" t="s">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="K21" s="39" t="s">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="L21" s="49"/>
     </row>
     <row r="22" spans="2:12">
       <c r="B22" s="1"/>
       <c r="C22" s="17" t="s">
-        <v>124</v>
+        <v>195</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>125</v>
+        <v>196</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>126</v>
+        <v>197</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>127</v>
+        <v>198</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>128</v>
+        <v>199</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
       <c r="I22" s="38" t="s">
-        <v>83</v>
+        <v>152</v>
       </c>
       <c r="J22" s="38" t="s">
-        <v>130</v>
+        <v>201</v>
       </c>
       <c r="K22" s="38" t="s">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="L22" s="48"/>
     </row>
     <row r="23" spans="2:12">
       <c r="B23" s="44" t="s">
-        <v>152</v>
+        <v>202</v>
       </c>
       <c r="C23" s="45"/>
       <c r="D23" s="45"/>
@@ -2045,62 +2229,62 @@
     <row r="24" spans="2:12">
       <c r="B24" s="16"/>
       <c r="C24" s="21" t="s">
-        <v>131</v>
+        <v>203</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>132</v>
+        <v>204</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>133</v>
+        <v>205</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>72</v>
+        <v>142</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>134</v>
+        <v>206</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>135</v>
+        <v>207</v>
       </c>
       <c r="I24" s="38" t="s">
-        <v>136</v>
+        <v>208</v>
       </c>
       <c r="J24" s="38" t="s">
-        <v>137</v>
+        <v>209</v>
       </c>
       <c r="K24" s="38" t="s">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="L24" s="48"/>
     </row>
     <row r="25" spans="2:12">
       <c r="B25" s="8"/>
       <c r="C25" s="21" t="s">
-        <v>138</v>
+        <v>210</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>139</v>
+        <v>211</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>140</v>
+        <v>212</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>141</v>
+        <v>213</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>73</v>
+        <v>143</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>142</v>
+        <v>214</v>
       </c>
       <c r="I25" s="39" t="s">
-        <v>75</v>
+        <v>145</v>
       </c>
       <c r="J25" s="39" t="s">
-        <v>143</v>
+        <v>215</v>
       </c>
       <c r="K25" s="39" t="s">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="L25" s="49"/>
     </row>
@@ -2108,13 +2292,16 @@
   <mergeCells count="1">
     <mergeCell ref="B2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="3"/>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{374E8FDA-6AAE-4C92-B5C4-D82A92134EB4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
   <dimension ref="B2:L25"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
@@ -2132,57 +2319,57 @@
     <col min="12" max="12" width="8.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="22.2">
-      <c r="B2" s="50" t="s">
-        <v>144</v>
-      </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
+    <row r="2" spans="2:12" ht="22.2" customHeight="1">
+      <c r="B2" s="54" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
     </row>
     <row r="3" spans="2:12">
       <c r="B3" s="23"/>
       <c r="C3" s="23" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="E3" s="24" t="s">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="F3" s="24" t="s">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="G3" s="24" t="s">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="H3" s="24" t="s">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="I3" s="24" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="J3" s="24" t="s">
-        <v>7</v>
+        <v>75</v>
       </c>
       <c r="K3" s="24" t="s">
-        <v>8</v>
+        <v>76</v>
       </c>
       <c r="L3" s="24" t="s">
-        <v>9</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="2:12">
       <c r="B4" s="46" t="s">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="C4" s="47"/>
       <c r="D4" s="47"/>
@@ -2195,172 +2382,172 @@
       <c r="K4" s="47"/>
       <c r="L4" s="47"/>
     </row>
-    <row r="5" spans="2:12" ht="30">
+    <row r="5" spans="2:12" ht="30" customHeight="1">
       <c r="B5" s="1"/>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>14</v>
+        <v>83</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
       <c r="I5" s="38" t="s">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="J5" s="38" t="s">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="K5" s="38" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="L5" s="36" t="s">
-        <v>145</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="2:12">
       <c r="B6" s="31"/>
       <c r="C6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F6" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="33" t="s">
-        <v>22</v>
-      </c>
       <c r="G6" s="34" t="s">
-        <v>23</v>
+        <v>92</v>
       </c>
       <c r="H6" s="35" t="s">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="I6" s="39" t="s">
-        <v>25</v>
+        <v>94</v>
       </c>
       <c r="J6" s="39" t="s">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="K6" s="39" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="L6" s="37"/>
     </row>
-    <row r="7" spans="2:12" ht="30">
+    <row r="7" spans="2:12" ht="30" customHeight="1">
       <c r="B7" s="1"/>
       <c r="C7" s="2" t="s">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>28</v>
+        <v>97</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>31</v>
+        <v>100</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>32</v>
+        <v>101</v>
       </c>
       <c r="I7" s="38" t="s">
-        <v>33</v>
+        <v>102</v>
       </c>
       <c r="J7" s="38" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="K7" s="38" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="L7" s="36" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" ht="30">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="30" customHeight="1">
       <c r="B8" s="31"/>
       <c r="C8" s="2" t="s">
-        <v>35</v>
+        <v>105</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>36</v>
+        <v>106</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>37</v>
+        <v>107</v>
       </c>
       <c r="F8" s="33" t="s">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>39</v>
+        <v>109</v>
       </c>
       <c r="H8" s="35" t="s">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="I8" s="39" t="s">
-        <v>41</v>
+        <v>111</v>
       </c>
       <c r="J8" s="39" t="s">
-        <v>42</v>
+        <v>112</v>
       </c>
       <c r="K8" s="39" t="s">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="L8" s="37" t="s">
-        <v>147</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="60" customHeight="1">
       <c r="B9" s="25"/>
       <c r="C9" s="2" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>45</v>
+        <v>115</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>46</v>
+        <v>116</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>47</v>
+        <v>117</v>
       </c>
       <c r="G9" s="28" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="H9" s="29" t="s">
-        <v>49</v>
+        <v>118</v>
       </c>
       <c r="I9" s="38" t="s">
-        <v>50</v>
+        <v>119</v>
       </c>
       <c r="J9" s="38" t="s">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="K9" s="38" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="L9" s="36" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="2:12">
       <c r="B10" s="40" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="C10" s="41"/>
       <c r="D10" s="41"/>
@@ -2373,133 +2560,133 @@
       <c r="K10" s="41"/>
       <c r="L10" s="41"/>
     </row>
-    <row r="11" spans="2:12" ht="30">
+    <row r="11" spans="2:12" ht="30" customHeight="1">
       <c r="B11" s="1"/>
       <c r="C11" s="13" t="s">
-        <v>52</v>
+        <v>123</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>53</v>
+        <v>124</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>54</v>
+        <v>125</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>55</v>
+        <v>126</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>56</v>
+        <v>127</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>57</v>
+        <v>128</v>
       </c>
       <c r="I11" s="38" t="s">
-        <v>58</v>
+        <v>129</v>
       </c>
       <c r="J11" s="38" t="s">
-        <v>59</v>
+        <v>130</v>
       </c>
       <c r="K11" s="38" t="s">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="L11" s="38"/>
     </row>
     <row r="12" spans="2:12" ht="45" customHeight="1">
       <c r="B12" s="15"/>
       <c r="C12" s="13" t="s">
-        <v>61</v>
+        <v>131</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>62</v>
+        <v>132</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>63</v>
+        <v>133</v>
       </c>
       <c r="F12" s="33" t="s">
-        <v>64</v>
+        <v>134</v>
       </c>
       <c r="G12" s="34" t="s">
-        <v>65</v>
+        <v>135</v>
       </c>
       <c r="H12" s="35" t="s">
-        <v>66</v>
+        <v>136</v>
       </c>
       <c r="I12" s="39" t="s">
-        <v>67</v>
+        <v>137</v>
       </c>
       <c r="J12" s="39" t="s">
-        <v>68</v>
+        <v>138</v>
       </c>
       <c r="K12" s="39" t="s">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="L12" s="39"/>
     </row>
     <row r="13" spans="2:12" ht="60" customHeight="1">
       <c r="B13" s="1"/>
       <c r="C13" s="13" t="s">
-        <v>69</v>
+        <v>139</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>71</v>
+        <v>141</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>72</v>
+        <v>142</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>73</v>
+        <v>143</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>74</v>
+        <v>144</v>
       </c>
       <c r="I13" s="38" t="s">
-        <v>75</v>
+        <v>145</v>
       </c>
       <c r="J13" s="38" t="s">
-        <v>76</v>
+        <v>146</v>
       </c>
       <c r="K13" s="38" t="s">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="L13" s="38"/>
     </row>
-    <row r="14" spans="2:12" ht="30">
+    <row r="14" spans="2:12" ht="30" customHeight="1">
       <c r="B14" s="15"/>
       <c r="C14" s="13" t="s">
-        <v>77</v>
+        <v>147</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>79</v>
+        <v>149</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="I14" s="39" t="s">
-        <v>83</v>
+        <v>152</v>
       </c>
       <c r="J14" s="39" t="s">
-        <v>84</v>
+        <v>153</v>
       </c>
       <c r="K14" s="39" t="s">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="L14" s="39"/>
     </row>
     <row r="15" spans="2:12">
       <c r="B15" s="42" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C15" s="43"/>
       <c r="D15" s="43"/>
@@ -2512,226 +2699,226 @@
       <c r="K15" s="43"/>
       <c r="L15" s="43"/>
     </row>
-    <row r="16" spans="2:12" ht="30">
+    <row r="16" spans="2:12" ht="30" customHeight="1">
       <c r="B16" s="1"/>
       <c r="C16" s="17" t="s">
-        <v>85</v>
+        <v>155</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>86</v>
+        <v>156</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>87</v>
+        <v>157</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>88</v>
+        <v>158</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>89</v>
+        <v>159</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="I16" s="38" t="s">
-        <v>91</v>
+        <v>161</v>
       </c>
       <c r="J16" s="38" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="K16" s="38" t="s">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="L16" s="38"/>
     </row>
-    <row r="17" spans="2:12" ht="30">
+    <row r="17" spans="2:12" ht="30" customHeight="1">
       <c r="B17" s="15"/>
       <c r="C17" s="17" t="s">
-        <v>92</v>
+        <v>163</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>93</v>
+        <v>164</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>94</v>
+        <v>165</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>95</v>
+        <v>166</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>96</v>
+        <v>167</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>97</v>
+        <v>168</v>
       </c>
       <c r="I17" s="39" t="s">
-        <v>98</v>
+        <v>169</v>
       </c>
       <c r="J17" s="39" t="s">
-        <v>99</v>
+        <v>170</v>
       </c>
       <c r="K17" s="39" t="s">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="L17" s="39"/>
     </row>
     <row r="18" spans="2:12">
       <c r="B18" s="1"/>
       <c r="C18" s="17" t="s">
-        <v>100</v>
+        <v>171</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>101</v>
+        <v>172</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>72</v>
+        <v>142</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>103</v>
+        <v>174</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>104</v>
+        <v>175</v>
       </c>
       <c r="I18" s="38" t="s">
-        <v>105</v>
+        <v>176</v>
       </c>
       <c r="J18" s="38" t="s">
-        <v>106</v>
+        <v>177</v>
       </c>
       <c r="K18" s="38" t="s">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="L18" s="38"/>
     </row>
-    <row r="19" spans="2:12" ht="30">
+    <row r="19" spans="2:12" ht="30" customHeight="1">
       <c r="B19" s="15"/>
       <c r="C19" s="17" t="s">
-        <v>107</v>
+        <v>178</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>108</v>
+        <v>179</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>109</v>
+        <v>180</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>72</v>
+        <v>142</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>110</v>
+        <v>181</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>111</v>
+        <v>182</v>
       </c>
       <c r="I19" s="39" t="s">
-        <v>112</v>
+        <v>183</v>
       </c>
       <c r="J19" s="39" t="s">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="K19" s="39" t="s">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="L19" s="39"/>
     </row>
-    <row r="20" spans="2:12" ht="30">
+    <row r="20" spans="2:12" ht="30" customHeight="1">
       <c r="B20" s="1"/>
       <c r="C20" s="17" t="s">
-        <v>113</v>
+        <v>184</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>114</v>
+        <v>185</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>115</v>
+        <v>186</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>116</v>
+        <v>187</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>117</v>
+        <v>188</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>118</v>
+        <v>189</v>
       </c>
       <c r="I20" s="38" t="s">
-        <v>119</v>
+        <v>190</v>
       </c>
       <c r="J20" s="38" t="s">
-        <v>68</v>
+        <v>138</v>
       </c>
       <c r="K20" s="38" t="s">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="L20" s="38"/>
     </row>
-    <row r="21" spans="2:12" ht="32.4">
+    <row r="21" spans="2:12" ht="32.4" customHeight="1">
       <c r="B21" s="15"/>
       <c r="C21" s="17" t="s">
-        <v>120</v>
+        <v>191</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>121</v>
+        <v>192</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>122</v>
+        <v>193</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>72</v>
+        <v>142</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>73</v>
+        <v>143</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>123</v>
+        <v>194</v>
       </c>
       <c r="I21" s="39" t="s">
-        <v>75</v>
+        <v>145</v>
       </c>
       <c r="J21" s="39" t="s">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="K21" s="39" t="s">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="L21" s="39"/>
     </row>
     <row r="22" spans="2:12">
       <c r="B22" s="1"/>
       <c r="C22" s="17" t="s">
-        <v>124</v>
+        <v>195</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>125</v>
+        <v>196</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>126</v>
+        <v>197</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>127</v>
+        <v>198</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>128</v>
+        <v>199</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
       <c r="I22" s="38" t="s">
-        <v>83</v>
+        <v>152</v>
       </c>
       <c r="J22" s="38" t="s">
-        <v>130</v>
+        <v>201</v>
       </c>
       <c r="K22" s="38" t="s">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="L22" s="38"/>
     </row>
     <row r="23" spans="2:12">
       <c r="B23" s="44" t="s">
-        <v>152</v>
+        <v>202</v>
       </c>
       <c r="C23" s="45"/>
       <c r="D23" s="45"/>
@@ -2747,62 +2934,62 @@
     <row r="24" spans="2:12">
       <c r="B24" s="16"/>
       <c r="C24" s="21" t="s">
-        <v>131</v>
+        <v>203</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>132</v>
+        <v>204</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>133</v>
+        <v>205</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>72</v>
+        <v>142</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>134</v>
+        <v>206</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>135</v>
+        <v>207</v>
       </c>
       <c r="I24" s="38" t="s">
-        <v>136</v>
+        <v>208</v>
       </c>
       <c r="J24" s="38" t="s">
-        <v>137</v>
+        <v>209</v>
       </c>
       <c r="K24" s="38" t="s">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="L24" s="38"/>
     </row>
     <row r="25" spans="2:12">
       <c r="B25" s="8"/>
       <c r="C25" s="21" t="s">
-        <v>138</v>
+        <v>210</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>139</v>
+        <v>211</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>140</v>
+        <v>212</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>141</v>
+        <v>213</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>73</v>
+        <v>143</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>142</v>
+        <v>214</v>
       </c>
       <c r="I25" s="39" t="s">
-        <v>75</v>
+        <v>145</v>
       </c>
       <c r="J25" s="39" t="s">
-        <v>143</v>
+        <v>215</v>
       </c>
       <c r="K25" s="39" t="s">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="L25" s="39"/>
     </row>
@@ -2816,227 +3003,584 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91979041-D559-4369-B044-F42A36666AF5}">
-  <dimension ref="B2:B44"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF534AB7"/>
+  </sheetPr>
+  <dimension ref="B1:D84"/>
   <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="4.09765625" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="6" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="2:2">
-      <c r="B2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2">
-      <c r="B3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2">
-      <c r="B4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2">
-      <c r="B5" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2">
-      <c r="B6" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2">
-      <c r="B7" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2">
-      <c r="B8" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2">
-      <c r="B9" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="10" spans="2:2">
-      <c r="B10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="11" spans="2:2">
-      <c r="B11" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="12" spans="2:2">
-      <c r="B12" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="13" spans="2:2">
-      <c r="B13" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="14" spans="2:2">
-      <c r="B14" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="15" spans="2:2">
-      <c r="B15" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="16" spans="2:2">
-      <c r="B16" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2">
-      <c r="B17" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2">
-      <c r="B18" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2">
-      <c r="B19" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2">
-      <c r="B20" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2">
-      <c r="B21" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="22" spans="2:2">
-      <c r="B22" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2">
-      <c r="B23" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2">
-      <c r="B24" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2">
-      <c r="B25" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="26" spans="2:2">
-      <c r="B26" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="27" spans="2:2">
-      <c r="B27" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="28" spans="2:2">
-      <c r="B28" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2">
-      <c r="B29" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="30" spans="2:2">
-      <c r="B30" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2">
-      <c r="B31" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2">
-      <c r="B32" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2">
-      <c r="B33" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2">
-      <c r="B34" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2">
-      <c r="B35" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2">
-      <c r="B36" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="37" spans="2:2">
-      <c r="B37" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="38" spans="2:2">
-      <c r="B38" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="39" spans="2:2">
-      <c r="B39" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="40" spans="2:2">
-      <c r="B40" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="41" spans="2:2">
-      <c r="B41" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="42" spans="2:2">
-      <c r="B42" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="43" spans="2:2">
-      <c r="B43" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="44" spans="2:2">
-      <c r="B44" t="s">
-        <v>187</v>
-      </c>
-    </row>
+    <row r="1" spans="2:4" ht="6" customHeight="1"/>
+    <row r="2" spans="2:4" ht="22.2" customHeight="1">
+      <c r="B2" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+    </row>
+    <row r="3" spans="2:4" ht="6" customHeight="1"/>
+    <row r="4" spans="2:4" ht="18" customHeight="1">
+      <c r="B4" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+    </row>
+    <row r="5" spans="2:4" ht="18" customHeight="1">
+      <c r="B5" s="50" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="50" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="50" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" ht="24" customHeight="1">
+      <c r="B6" s="51" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+    </row>
+    <row r="7" spans="2:4" ht="12" customHeight="1">
+      <c r="B7" s="52" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
+    </row>
+    <row r="8" spans="2:4" ht="36" customHeight="1">
+      <c r="B8" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+    </row>
+    <row r="9" spans="2:4" ht="12" customHeight="1">
+      <c r="B9" s="52" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="52"/>
+      <c r="D9" s="52"/>
+    </row>
+    <row r="10" spans="2:4" ht="28.05" customHeight="1">
+      <c r="B10" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+    </row>
+    <row r="11" spans="2:4" ht="12" customHeight="1">
+      <c r="B11" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+    </row>
+    <row r="12" spans="2:4" ht="60">
+      <c r="B12" s="51"/>
+      <c r="C12" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="51"/>
+    </row>
+    <row r="13" spans="2:4" ht="12" customHeight="1">
+      <c r="B13" s="52"/>
+      <c r="C13" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="52"/>
+    </row>
+    <row r="14" spans="2:4" ht="36" customHeight="1">
+      <c r="B14" s="51" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+    </row>
+    <row r="15" spans="2:4" ht="6" customHeight="1"/>
+    <row r="16" spans="2:4" ht="16.05" customHeight="1">
+      <c r="B16" s="58" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="59"/>
+      <c r="D16" s="59"/>
+    </row>
+    <row r="17" spans="2:4" ht="30">
+      <c r="B17" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
+    </row>
+    <row r="18" spans="2:4" ht="12" customHeight="1">
+      <c r="B18" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
+    </row>
+    <row r="19" spans="2:4" ht="60">
+      <c r="B19" s="51"/>
+      <c r="C19" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="51"/>
+    </row>
+    <row r="20" spans="2:4" ht="12" customHeight="1">
+      <c r="B20" s="52"/>
+      <c r="C20" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="52"/>
+    </row>
+    <row r="21" spans="2:4" ht="24" customHeight="1">
+      <c r="B21" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="51"/>
+      <c r="D21" s="51"/>
+    </row>
+    <row r="22" spans="2:4" ht="6" customHeight="1"/>
+    <row r="23" spans="2:4" ht="16.05" customHeight="1">
+      <c r="B23" s="58" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="59"/>
+      <c r="D23" s="59"/>
+    </row>
+    <row r="24" spans="2:4" ht="22.05" customHeight="1">
+      <c r="B24" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="51"/>
+      <c r="D24" s="51"/>
+    </row>
+    <row r="25" spans="2:4" ht="12" customHeight="1">
+      <c r="B25" s="52" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="52"/>
+      <c r="D25" s="52"/>
+    </row>
+    <row r="26" spans="2:4" ht="36" customHeight="1">
+      <c r="B26" s="51"/>
+      <c r="C26" s="51" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26" s="51"/>
+    </row>
+    <row r="27" spans="2:4" ht="12" customHeight="1">
+      <c r="B27" s="52"/>
+      <c r="C27" s="52" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="52"/>
+    </row>
+    <row r="28" spans="2:4" ht="22.05" customHeight="1">
+      <c r="B28" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="C28" s="51"/>
+      <c r="D28" s="51"/>
+    </row>
+    <row r="29" spans="2:4" ht="6" customHeight="1"/>
+    <row r="30" spans="2:4" ht="16.05" customHeight="1">
+      <c r="B30" s="58" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" s="59"/>
+      <c r="D30" s="59"/>
+    </row>
+    <row r="31" spans="2:4" ht="40.049999999999997" customHeight="1">
+      <c r="B31" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31" s="51"/>
+      <c r="D31" s="51" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" ht="12" customHeight="1">
+      <c r="B32" s="52" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="52"/>
+      <c r="D32" s="52" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" ht="36" customHeight="1">
+      <c r="B33" s="51"/>
+      <c r="C33" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="D33" s="51"/>
+    </row>
+    <row r="34" spans="2:4" ht="12" customHeight="1">
+      <c r="B34" s="52"/>
+      <c r="C34" s="52" t="s">
+        <v>6</v>
+      </c>
+      <c r="D34" s="52"/>
+    </row>
+    <row r="35" spans="2:4" ht="28.05" customHeight="1">
+      <c r="B35" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" s="51"/>
+      <c r="D35" s="51" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" ht="10.050000000000001" customHeight="1"/>
+    <row r="37" spans="2:4" ht="18" customHeight="1">
+      <c r="B37" s="56" t="s">
+        <v>28</v>
+      </c>
+      <c r="C37" s="57"/>
+      <c r="D37" s="57"/>
+    </row>
+    <row r="38" spans="2:4" ht="18" customHeight="1">
+      <c r="B38" s="50" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="50" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="50" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" ht="36" customHeight="1">
+      <c r="B39" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="C39" s="51"/>
+      <c r="D39" s="51"/>
+    </row>
+    <row r="40" spans="2:4" ht="12" customHeight="1">
+      <c r="B40" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="C40" s="52"/>
+      <c r="D40" s="52"/>
+    </row>
+    <row r="41" spans="2:4" ht="60">
+      <c r="B41" s="51"/>
+      <c r="C41" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="D41" s="51"/>
+    </row>
+    <row r="42" spans="2:4" ht="12" customHeight="1">
+      <c r="B42" s="52"/>
+      <c r="C42" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="D42" s="52"/>
+    </row>
+    <row r="43" spans="2:4" ht="36" customHeight="1">
+      <c r="B43" s="51" t="s">
+        <v>33</v>
+      </c>
+      <c r="C43" s="51"/>
+      <c r="D43" s="51"/>
+    </row>
+    <row r="44" spans="2:4" ht="12" customHeight="1">
+      <c r="B44" s="52" t="s">
+        <v>34</v>
+      </c>
+      <c r="C44" s="52"/>
+      <c r="D44" s="52"/>
+    </row>
+    <row r="45" spans="2:4" ht="45">
+      <c r="B45" s="51"/>
+      <c r="C45" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D45" s="51"/>
+    </row>
+    <row r="46" spans="2:4" ht="12" customHeight="1">
+      <c r="B46" s="52"/>
+      <c r="C46" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="D46" s="52"/>
+    </row>
+    <row r="47" spans="2:4" ht="30" customHeight="1">
+      <c r="B47" s="51"/>
+      <c r="C47" s="51"/>
+      <c r="D47" s="51" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" ht="12" customHeight="1">
+      <c r="B48" s="52"/>
+      <c r="C48" s="52"/>
+      <c r="D48" s="52" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" ht="45">
+      <c r="B49" s="51"/>
+      <c r="C49" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="D49" s="51"/>
+    </row>
+    <row r="50" spans="2:4" ht="12" customHeight="1">
+      <c r="B50" s="52"/>
+      <c r="C50" s="52" t="s">
+        <v>40</v>
+      </c>
+      <c r="D50" s="52"/>
+    </row>
+    <row r="51" spans="2:4" ht="28.05" customHeight="1">
+      <c r="B51" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="C51" s="51"/>
+      <c r="D51" s="51" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4" ht="10.050000000000001" customHeight="1"/>
+    <row r="53" spans="2:4" ht="18" customHeight="1">
+      <c r="B53" s="56" t="s">
+        <v>43</v>
+      </c>
+      <c r="C53" s="57"/>
+      <c r="D53" s="57"/>
+    </row>
+    <row r="54" spans="2:4" ht="18" customHeight="1">
+      <c r="B54" s="50" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="50" t="s">
+        <v>3</v>
+      </c>
+      <c r="D54" s="50" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4" ht="36" customHeight="1">
+      <c r="B55" s="51" t="s">
+        <v>44</v>
+      </c>
+      <c r="C55" s="51"/>
+      <c r="D55" s="51"/>
+    </row>
+    <row r="56" spans="2:4" ht="12" customHeight="1">
+      <c r="B56" s="52" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="52"/>
+      <c r="D56" s="52"/>
+    </row>
+    <row r="57" spans="2:4" ht="45">
+      <c r="B57" s="51"/>
+      <c r="C57" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="D57" s="51"/>
+    </row>
+    <row r="58" spans="2:4" ht="12" customHeight="1">
+      <c r="B58" s="52"/>
+      <c r="C58" s="52" t="s">
+        <v>46</v>
+      </c>
+      <c r="D58" s="52"/>
+    </row>
+    <row r="59" spans="2:4" ht="45">
+      <c r="B59" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="C59" s="51" t="s">
+        <v>48</v>
+      </c>
+      <c r="D59" s="51"/>
+    </row>
+    <row r="60" spans="2:4" ht="12" customHeight="1">
+      <c r="B60" s="52" t="s">
+        <v>49</v>
+      </c>
+      <c r="C60" s="52"/>
+      <c r="D60" s="52"/>
+    </row>
+    <row r="61" spans="2:4" ht="45">
+      <c r="B61" s="51"/>
+      <c r="C61" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="D61" s="51"/>
+    </row>
+    <row r="62" spans="2:4" ht="12" customHeight="1">
+      <c r="B62" s="52"/>
+      <c r="C62" s="52" t="s">
+        <v>51</v>
+      </c>
+      <c r="D62" s="52"/>
+    </row>
+    <row r="63" spans="2:4" ht="36" customHeight="1">
+      <c r="B63" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="C63" s="51"/>
+      <c r="D63" s="51"/>
+    </row>
+    <row r="64" spans="2:4" ht="12" customHeight="1">
+      <c r="B64" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="C64" s="52"/>
+      <c r="D64" s="52"/>
+    </row>
+    <row r="65" spans="2:4" ht="45">
+      <c r="B65" s="51"/>
+      <c r="C65" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="D65" s="51"/>
+    </row>
+    <row r="66" spans="2:4" ht="12" customHeight="1">
+      <c r="B66" s="52"/>
+      <c r="C66" s="52" t="s">
+        <v>55</v>
+      </c>
+      <c r="D66" s="52"/>
+    </row>
+    <row r="67" spans="2:4" ht="30">
+      <c r="B67" s="51"/>
+      <c r="C67" s="51"/>
+      <c r="D67" s="51" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4" ht="12" customHeight="1">
+      <c r="B68" s="52"/>
+      <c r="C68" s="52"/>
+      <c r="D68" s="52" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4" ht="45">
+      <c r="B69" s="51"/>
+      <c r="C69" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="D69" s="51"/>
+    </row>
+    <row r="70" spans="2:4" ht="12" customHeight="1">
+      <c r="B70" s="52"/>
+      <c r="C70" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D70" s="52"/>
+    </row>
+    <row r="71" spans="2:4" ht="24" customHeight="1">
+      <c r="B71" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="C71" s="51"/>
+      <c r="D71" s="51" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4" ht="10.050000000000001" customHeight="1"/>
+    <row r="73" spans="2:4" ht="18" customHeight="1">
+      <c r="B73" s="56" t="s">
+        <v>61</v>
+      </c>
+      <c r="C73" s="57"/>
+      <c r="D73" s="57"/>
+    </row>
+    <row r="74" spans="2:4" ht="18" customHeight="1">
+      <c r="B74" s="50" t="s">
+        <v>2</v>
+      </c>
+      <c r="C74" s="50" t="s">
+        <v>3</v>
+      </c>
+      <c r="D74" s="50" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="2:4" ht="36" customHeight="1">
+      <c r="B75" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C75" s="51"/>
+      <c r="D75" s="51"/>
+    </row>
+    <row r="76" spans="2:4" ht="12" customHeight="1">
+      <c r="B76" s="52"/>
+      <c r="C76" s="52"/>
+      <c r="D76" s="52"/>
+    </row>
+    <row r="77" spans="2:4" ht="40.049999999999997" customHeight="1">
+      <c r="B77" s="51"/>
+      <c r="C77" s="51" t="s">
+        <v>63</v>
+      </c>
+      <c r="D77" s="51"/>
+    </row>
+    <row r="78" spans="2:4" ht="12" customHeight="1">
+      <c r="B78" s="52"/>
+      <c r="C78" s="52" t="s">
+        <v>6</v>
+      </c>
+      <c r="D78" s="52"/>
+    </row>
+    <row r="79" spans="2:4" ht="36" customHeight="1">
+      <c r="B79" s="51"/>
+      <c r="C79" s="51"/>
+      <c r="D79" s="51" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="80" spans="2:4" ht="12" customHeight="1">
+      <c r="B80" s="52"/>
+      <c r="C80" s="52"/>
+      <c r="D80" s="52"/>
+    </row>
+    <row r="81" spans="2:4" ht="36" customHeight="1">
+      <c r="B81" s="51"/>
+      <c r="C81" s="51" t="s">
+        <v>65</v>
+      </c>
+      <c r="D81" s="51"/>
+    </row>
+    <row r="82" spans="2:4" ht="6" customHeight="1"/>
+    <row r="83" spans="2:4" ht="25.95" customHeight="1">
+      <c r="B83" s="53" t="s">
+        <v>66</v>
+      </c>
+      <c r="C83" s="51"/>
+      <c r="D83" s="51"/>
+    </row>
+    <row r="84" spans="2:4" ht="10.050000000000001" customHeight="1"/>
   </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B73:D73"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B16:D16"/>
+  </mergeCells>
   <phoneticPr fontId="2"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>